--- a/data.xlsx
+++ b/data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_sokutei/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0F3E355-A466-234C-9212-AC0BFC883056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768C424F-BA04-854E-BBF6-00C6B9EA9284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="680" windowWidth="28060" windowHeight="17240" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,14 +36,153 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>ch</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>エネルギー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>回帰統計</t>
+  </si>
+  <si>
+    <t>重相関 R</t>
+  </si>
+  <si>
+    <t>重決定 R2</t>
+  </si>
+  <si>
+    <t>補正 R2</t>
+  </si>
+  <si>
+    <t>標準誤差</t>
+  </si>
+  <si>
+    <t>観測数</t>
+  </si>
+  <si>
+    <t>分散分析表</t>
+  </si>
+  <si>
+    <t>回帰</t>
+  </si>
+  <si>
+    <t>残差</t>
+  </si>
+  <si>
+    <t>合計</t>
+  </si>
+  <si>
+    <t>切片</t>
+  </si>
+  <si>
+    <t>自由度</t>
+  </si>
+  <si>
+    <t>変動</t>
+  </si>
+  <si>
+    <t>分散</t>
+  </si>
+  <si>
+    <t>観測された分散比</t>
+  </si>
+  <si>
+    <t>有意 F</t>
+  </si>
+  <si>
+    <t>係数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t </t>
+  </si>
+  <si>
+    <t>P-値</t>
+  </si>
+  <si>
+    <t>下限 95%</t>
+  </si>
+  <si>
+    <t>上限 95%</t>
+  </si>
+  <si>
+    <t>下限 95.0%</t>
+  </si>
+  <si>
+    <t>上限 95.0%</t>
+  </si>
+  <si>
+    <t>X 値 1</t>
+  </si>
+  <si>
+    <t>傾き</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">カタムキ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>切片</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">セッペン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cs137</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予測値</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ヨソクチ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誤差</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ゴサ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>伝搬誤差</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">デンパン </t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t xml:space="preserve">ゴサ </t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -75,12 +215,32 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -89,9 +249,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -108,6 +280,935 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$3:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>336</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>308</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>350</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$3:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1275</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>511</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1173</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2053-7940-9129-4E43EC4777CE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="780788927"/>
+        <c:axId val="780790719"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="780788927"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="780790719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="780790719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="780788927"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>831850</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEBE1E1E-C236-02E0-EFD9-F3D65908FB25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,10 +1528,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDDC4F7-1C94-C84E-928F-3F14F658D6C5}">
-  <dimension ref="B2:C7"/>
+  <dimension ref="A2:F12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="1:6">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -438,31 +1539,55 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="1:6">
       <c r="B3">
         <v>336</v>
       </c>
       <c r="C3">
         <v>1275</v>
       </c>
-    </row>
-    <row r="4" spans="2:3">
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="B4">
         <v>138</v>
       </c>
       <c r="C4">
         <v>511</v>
       </c>
-    </row>
-    <row r="5" spans="2:3">
+      <c r="E4" cm="1">
+        <f t="array" ref="E4:F4">LINEST(C3:C7,B3:B7,TRUE,FALSE)</f>
+        <v>3.8488775604213354</v>
+      </c>
+      <c r="F4">
+        <v>-15.528022602339774</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="B5">
         <v>35</v>
       </c>
       <c r="C5">
         <v>122</v>
       </c>
-    </row>
-    <row r="6" spans="2:3">
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5">
+        <f>Sheet2!C18</f>
+        <v>1.4305982448012507E-2</v>
+      </c>
+      <c r="F5">
+        <f>Sheet2!C17</f>
+        <v>3.7878664857879132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="B6">
         <v>308</v>
       </c>
@@ -470,12 +1595,264 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="7" spans="2:3">
+    <row r="7" spans="1:6">
       <c r="B7">
         <v>350</v>
       </c>
       <c r="C7">
         <v>1333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9">
+        <v>178</v>
+      </c>
+      <c r="C9">
+        <v>661.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <f>E4*B9+F4</f>
+        <v>669.57218315265789</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12">
+        <f>SQRT((B9*E5)^2+F5^2)</f>
+        <v>4.5642541425258649</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F55B58-FE65-1649-820B-550CCEC4C2C0}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="21" thickBot="1"/>
+    <row r="3" spans="1:9">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.9999792773666133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.99995855516265408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.99994474021687207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3.9993140911977223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="21" thickBot="1">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="21" thickBot="1">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1157720.8164603997</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1157720.8164603997</v>
+      </c>
+      <c r="E12" s="1">
+        <v>72382.372753713295</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1.132400162722055E-7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1">
+        <v>47.983539600157989</v>
+      </c>
+      <c r="D13" s="1">
+        <v>15.994513200052664</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="21" thickBot="1">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1157768.7999999998</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="21" thickBot="1"/>
+    <row r="16" spans="1:9">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-15.528022602339774</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3.7878664857879132</v>
+      </c>
+      <c r="D17" s="1">
+        <v>-4.0994112808888499</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2.6260344312889514E-2</v>
+      </c>
+      <c r="F17" s="1">
+        <v>-27.582704304943505</v>
+      </c>
+      <c r="G17" s="1">
+        <v>-3.4733408997360429</v>
+      </c>
+      <c r="H17" s="1">
+        <v>-27.582704304943505</v>
+      </c>
+      <c r="I17" s="1">
+        <v>-3.4733408997360429</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="21" thickBot="1">
+      <c r="A18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="2">
+        <v>3.8488775604213354</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1.4305982448012507E-2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>269.03972337503109</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.132400162722055E-7</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3.8033495394362045</v>
+      </c>
+      <c r="G18" s="2">
+        <v>3.8944055814064664</v>
+      </c>
+      <c r="H18" s="2">
+        <v>3.8033495394362045</v>
+      </c>
+      <c r="I18" s="2">
+        <v>3.8944055814064664</v>
       </c>
     </row>
   </sheetData>
